--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10114"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lewisspurgin/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/x0504807/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{D46A0444-0E40-774E-AA66-7FA7C038F3F1}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DA0087-C3D6-0C45-8130-8B27B51D98D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="22240" windowHeight="10640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="87">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
@@ -292,7 +292,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +304,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -326,15 +334,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -761,6 +772,9 @@
       <c r="B13" t="s">
         <v>11</v>
       </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -879,6 +893,9 @@
       <c r="B24" t="s">
         <v>22</v>
       </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -928,6 +945,9 @@
       <c r="B29" t="s">
         <v>27</v>
       </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -974,7 +994,7 @@
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1045,7 +1065,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B34" r:id="rId1" xr:uid="{692DA58F-34E0-9248-9792-92FFFAA4C795}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/x0504807/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DA0087-C3D6-0C45-8130-8B27B51D98D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5497C5E5-C6E4-8D42-BDFF-0D05354F920F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="22240" windowHeight="10640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="460" windowWidth="32580" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="130">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
   <si>
-    <t>Eduardo Belda &lt;ebelda@dca.upv.es&gt;,</t>
-  </si>
-  <si>
     <t>Andrey Bushuev &lt;a_bushuev@mail.ru&gt;,</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>Janos Torok &lt;yeti01@elte.hu&gt;,</t>
   </si>
   <si>
-    <t>Teru YUTA &lt;tyuta@fsc.hokudai.ac.jp&gt;,</t>
-  </si>
-  <si>
     <t>albayraktamer@gmail.com,</t>
   </si>
   <si>
@@ -159,9 +153,6 @@
     <t>Christos Barboutis</t>
   </si>
   <si>
-    <t xml:space="preserve"> Eduardo Belda</t>
-  </si>
-  <si>
     <t>Andrey Bushuev</t>
   </si>
   <si>
@@ -186,9 +177,6 @@
     <t>Kjell Einar Erikstad</t>
   </si>
   <si>
-    <t>Slava Fedorov</t>
-  </si>
-  <si>
     <t>Matteo Griggio</t>
   </si>
   <si>
@@ -216,21 +204,12 @@
     <t>Laura Kvist</t>
   </si>
   <si>
-    <t>Raivo Mand</t>
-  </si>
-  <si>
     <t>Erik Matthysen</t>
   </si>
   <si>
     <t>Ruedi Nager</t>
   </si>
   <si>
-    <t>Boris Nikolov</t>
-  </si>
-  <si>
-    <t>Claudia Norte</t>
-  </si>
-  <si>
     <t>Markku Orell</t>
   </si>
   <si>
@@ -255,15 +234,9 @@
     <t>Joost Tinbergen</t>
   </si>
   <si>
-    <t>Janos Torok</t>
-  </si>
-  <si>
     <t>Barbara Tschirren</t>
   </si>
   <si>
-    <t xml:space="preserve">Csongor Vágási </t>
-  </si>
-  <si>
     <t>Teru Yuta</t>
   </si>
   <si>
@@ -285,14 +258,170 @@
     <t>y</t>
   </si>
   <si>
-    <t>Heard from Bart - address probably needs changing</t>
+    <t>Zvenigorod Biological Station of Lomonosov Moscow State University, P.O. Box Shikhovo, Odintsovo District, Moscow 143092, Russia.</t>
+  </si>
+  <si>
+    <t>ivankinalena@yandex.ru</t>
+  </si>
+  <si>
+    <t>Elena Ivankina</t>
+  </si>
+  <si>
+    <t>Address 1</t>
+  </si>
+  <si>
+    <t>Address 2</t>
+  </si>
+  <si>
+    <t>Evolutionary Ecology Group, University of Antwerp, Groenenborgerlaan 171, B-2020, Antwerpen, Belgium</t>
+  </si>
+  <si>
+    <t>Institut d'Investigació per a la Gestió Integrada de Zones Costaneres, Campus de Gandia, Universitat Politècnica de València, Carrer Paranimf 1, E-46730 Grau de Gandia (València), Spain</t>
+  </si>
+  <si>
+    <t>Faculty of Biology, Lomonosov Moscow State University, Moscow 119234, Russia</t>
+  </si>
+  <si>
+    <t>Vyacheslav Fedorov</t>
+  </si>
+  <si>
+    <t>Dipartimento di Scienze e Politiche Ambientali, Università degli Studi di Milano, via Celoria 26, I-20133, Milano, Italy</t>
+  </si>
+  <si>
+    <t>Department of Biology, University of Padova, Via U. Bassi 58/B, I-35131, Padova, Italy</t>
+  </si>
+  <si>
+    <t>Area Avifauna Migratrice, Istituto Superiore per la Protezione e la Ricerca Ambientale (ISPRA), via Ca’ Fornacetta 9, I-40064, Ozzano Emilia, (BO), Italy</t>
+  </si>
+  <si>
+    <t>Institute of Environmental Sciences, Jagiellonian University, Gronostajowa 7, 30-387 Kraków, Poland.</t>
+  </si>
+  <si>
+    <t>Behavioural Ecology, Department of Biology, Ludwig Maximilians University of Munich, Planegg-Martinsried, Germany</t>
+  </si>
+  <si>
+    <t>UMR CNRS 5558—LBBE, Biométrie et Biologie Évolutive, UCB Lyon 1 - Bât. Grégor Mendel, 43 bd du 11 novembre 1918, 69622 VILLEURBANNE cedex, France.</t>
+  </si>
+  <si>
+    <t>Department of Ecology and Evolution, Animal Ecology, Evolutionary Biology Centre, Uppsala University, Sweden</t>
+  </si>
+  <si>
+    <t>Department of Biology, University of Turku, Turku 20014, Finland.</t>
+  </si>
+  <si>
+    <t>Norwegian Institute for Nature Research, FRAM-High North Research Centre for Climate and the Environment, 9296 Tromsø, Norway.</t>
+  </si>
+  <si>
+    <t>CEFE-CNRS, UMR 5175, 1919, route de Mende, F34293 Montpellier Cedex 5, France.</t>
+  </si>
+  <si>
+    <t>Max Planck Institute for Ornithology, Department of Behavioural Ecology &amp; Evolutionary Genetics, Eberhard-Gwinner-Straße, House 5, 82319 Seewiesen (Starnberg), Germany</t>
+  </si>
+  <si>
+    <t>Institute of Wildlife Biology and Game Management, University of Natural Resources and Life Science, A-1180 Vienna, Austria.</t>
+  </si>
+  <si>
+    <t>Address 3</t>
+  </si>
+  <si>
+    <t>Interuniversity Institute for Biostatistics and statistical Bioinformatics, Hasselt University, Diepenbeek, Belgium</t>
+  </si>
+  <si>
+    <t>Department of Ecology and Evolutionary Biology, Princeton University, Princeton, NJ, United States of America</t>
+  </si>
+  <si>
+    <t>Max Planck Institute for Ornithology, Department of Behavioural Ecology &amp; Evolutionary Genetics, Eberhard-Gwinner-Straße, House 5, 82319 Seewiesen (Starnberg), Germany.</t>
+  </si>
+  <si>
+    <t>Faculty of Biology, Lomonosov Moscow State University, Moscow 119234, Russia.</t>
+  </si>
+  <si>
+    <t>Department of Zoology and Laboratory of Ornithology, Faculty of Science, Palacký University, Olomouc 77147, Czech Republic</t>
+  </si>
+  <si>
+    <t>Department of Ecology and Genetics, P.O.Box 3000, 90014-University of Oulu, Finland</t>
+  </si>
+  <si>
+    <t>Raivo Mänd</t>
+  </si>
+  <si>
+    <t>Department of Zoology, Institute of Ecology and Earth Sciences, University of Tartu, Vanemuise 46, Tartu 51014, Estonia</t>
+  </si>
+  <si>
+    <t>Behavioural Ecology Group, Department of Animal Sciences, Wageningen University, Wageningen 6708 PB, The Netherlands.</t>
+  </si>
+  <si>
+    <t>Institute of Biodiversity, Animal Health and Comparative Medicine, University of Glasgow, Glasgow G12 8QQ, UK.</t>
+  </si>
+  <si>
+    <t>A. Claudia Norte</t>
+  </si>
+  <si>
+    <t>MARE - Marine and Environmental Sciences Centre, Department of Life Sciences, Faculty of Sciences and Technology, University of Coimbra. Portugal</t>
+  </si>
+  <si>
+    <t>Evolutionary Ecology Lab, Institute of Ecology and Evolution, University of Bern, Bern 3012, Switzerland</t>
+  </si>
+  <si>
+    <t>Centre for Ecological and Evolutionary Synthesis (CEES), Department of Biosciences, University of Oslo, P.O. Box 1066, Blindern, 0316 Oslo, Norway.</t>
+  </si>
+  <si>
+    <t>Department of Zoology, Institute of Ecology and Earth Sciences, University of Tartu, Vanemuise 46, Tartu 51014, Estonia.</t>
+  </si>
+  <si>
+    <t>Centre for Ecological and Evolutionary Studies (CEES), Univ. of Groningen, PO Box 11103, NL-9700 CC Groningen, The Netherlands.</t>
+  </si>
+  <si>
+    <t>János Török</t>
+  </si>
+  <si>
+    <t>Behavioural Ecology Group, Department of Systematic Zoology and Ecology, Eötvös Loránd University, Budapest H-1117, Hungary.</t>
+  </si>
+  <si>
+    <t>Department of Biology, Mehmet Akif Ersoy University, Science and Art Faculty, Ortulu, Burdur, Turkey</t>
+  </si>
+  <si>
+    <t>Hellenic Ornithological Society / BirdLife Greece, Themistokleous 80, GR-10681 Athens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Csongor I. Vágási </t>
+  </si>
+  <si>
+    <t>Evolutionary Ecology Group, Hungarian Department of Biology and Ecology, Babeș-Bolyai University, Cluj-Napoca, Romania.</t>
+  </si>
+  <si>
+    <t>Behavioural Ecology Research Group, Department of Evolutionary Zoology, University of Debrecen, Debrecen, Hungary.</t>
+  </si>
+  <si>
+    <t>Institute of Biodiversity and Ecosystem Research, Bulgarian Academy of Sciences, 1 Tsar Osvoboditel Blvd, 1000 Sofia, Bulgaria</t>
+  </si>
+  <si>
+    <t>Boris P. Nikolov</t>
+  </si>
+  <si>
+    <t>University of Nevada, Reno, USA</t>
+  </si>
+  <si>
+    <t>University of Exeter, Centre for Ecology and Conservation, Treliever Road, Penryn, TR10 9FE, United Kingdom</t>
+  </si>
+  <si>
+    <t>Graduate School of Environmental Science, Hokkaido University, N10 W5 Sapporo, Hokkaido 060-0810, Japan</t>
+  </si>
+  <si>
+    <t>tyuta@fsc.hokudai.ac.jp</t>
+  </si>
+  <si>
+    <t>Eduardo Belda</t>
+  </si>
+  <si>
+    <t>ebelda@dca.upv.es</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,14 +433,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,18 +455,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -624,449 +741,622 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.83203125" customWidth="1"/>
-    <col min="2" max="2" width="53.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="143" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="87.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="86.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>51</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>52</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>54</v>
       </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>67</v>
       </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>68</v>
       </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="B37" t="s">
         <v>28</v>
       </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="E37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="D38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="D40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>70</v>
       </c>
-      <c r="B39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" t="s">
-        <v>85</v>
+      <c r="B41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B34" r:id="rId1" xr:uid="{692DA58F-34E0-9248-9792-92FFFAA4C795}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{692DA58F-34E0-9248-9792-92FFFAA4C795}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>

--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/x0504807/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lewisspurgin/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5497C5E5-C6E4-8D42-BDFF-0D05354F920F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{B50FE7FE-2B73-B244-A7FC-22B97CE376E5}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="460" windowWidth="32580" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="2080" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="129">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
@@ -243,15 +243,6 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>Email returned</t>
-  </si>
-  <si>
-    <t>Away until 15/01/2019</t>
-  </si>
-  <si>
-    <t>Away until 22/01/2019</t>
-  </si>
-  <si>
     <t>Responded</t>
   </si>
   <si>
@@ -415,6 +406,12 @@
   </si>
   <si>
     <t>ebelda@dca.upv.es</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -764,16 +761,16 @@
         <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -783,11 +780,14 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -797,11 +797,14 @@
       <c r="B3" t="s">
         <v>30</v>
       </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -811,25 +814,31 @@
       <c r="B4" t="s">
         <v>31</v>
       </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" t="s">
         <v>128</v>
       </c>
-      <c r="B5" t="s">
-        <v>129</v>
-      </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -839,11 +848,14 @@
       <c r="B6" t="s">
         <v>1</v>
       </c>
+      <c r="C6" t="s">
+        <v>128</v>
+      </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -853,11 +865,14 @@
       <c r="B7" t="s">
         <v>2</v>
       </c>
+      <c r="C7" t="s">
+        <v>127</v>
+      </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -867,11 +882,8 @@
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -882,10 +894,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -896,10 +908,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -910,13 +922,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -927,10 +939,10 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -941,27 +953,27 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -971,11 +983,14 @@
       <c r="B15" t="s">
         <v>10</v>
       </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -986,10 +1001,10 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -999,11 +1014,14 @@
       <c r="B17" t="s">
         <v>13</v>
       </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1014,10 +1032,10 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1027,34 +1045,31 @@
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1065,10 +1080,10 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1079,10 +1094,10 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1093,10 +1108,10 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1107,24 +1122,24 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1134,11 +1149,14 @@
       <c r="B26" t="s">
         <v>20</v>
       </c>
+      <c r="C26" t="s">
+        <v>127</v>
+      </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1149,38 +1167,38 @@
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1191,10 +1209,10 @@
         <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1205,13 +1223,13 @@
         <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1222,10 +1240,10 @@
         <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1236,10 +1254,10 @@
         <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1249,11 +1267,14 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
+      <c r="C34" t="s">
+        <v>127</v>
+      </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1264,10 +1285,10 @@
         <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1278,10 +1299,10 @@
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1292,21 +1313,21 @@
         <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1317,27 +1338,27 @@
         <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B40" t="s">
         <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1345,13 +1366,13 @@
         <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lewisspurgin/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{B50FE7FE-2B73-B244-A7FC-22B97CE376E5}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{A75D8D32-3F3C-EE47-A5E4-17C520FE1B9B}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="2080" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2080" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="129">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
@@ -893,6 +893,9 @@
       <c r="B9" t="s">
         <v>3</v>
       </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
       <c r="D9" t="s">
         <v>73</v>
       </c>
@@ -906,6 +909,9 @@
       </c>
       <c r="B10" t="s">
         <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
       </c>
       <c r="D10" t="s">
         <v>73</v>

--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10114"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lewisspurgin/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/x0504807/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{A75D8D32-3F3C-EE47-A5E4-17C520FE1B9B}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4FC7E2-1597-C944-8FB5-B9C569E70652}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2080" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2180" yWindow="1480" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="130">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
@@ -189,9 +189,6 @@
     <t xml:space="preserve"> Dieter Heylen</t>
   </si>
   <si>
-    <t>Camilla Hinde</t>
-  </si>
-  <si>
     <t>Bart Kempenaers</t>
   </si>
   <si>
@@ -412,6 +409,12 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>REMOVED</t>
+  </si>
+  <si>
+    <t>Camilla A. Hinde</t>
   </si>
 </sst>
 </file>
@@ -758,19 +761,19 @@
         <v>37</v>
       </c>
       <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
-        <v>72</v>
-      </c>
       <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
         <v>77</v>
       </c>
-      <c r="F1" t="s">
-        <v>78</v>
-      </c>
       <c r="G1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -781,13 +784,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -798,13 +801,13 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -815,30 +818,30 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" t="s">
         <v>125</v>
       </c>
-      <c r="B5" t="s">
-        <v>126</v>
-      </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -849,13 +852,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -866,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -882,8 +885,11 @@
       <c r="B8" t="s">
         <v>4</v>
       </c>
+      <c r="C8" t="s">
+        <v>126</v>
+      </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -894,13 +900,13 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -911,13 +917,13 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -927,14 +933,17 @@
       <c r="B11" t="s">
         <v>6</v>
       </c>
+      <c r="C11" t="s">
+        <v>126</v>
+      </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" t="s">
         <v>88</v>
-      </c>
-      <c r="F11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -944,11 +953,14 @@
       <c r="B12" t="s">
         <v>7</v>
       </c>
+      <c r="C12" t="s">
+        <v>126</v>
+      </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -958,28 +970,31 @@
       <c r="B13" t="s">
         <v>8</v>
       </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -990,13 +1005,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1006,11 +1021,14 @@
       <c r="B16" t="s">
         <v>11</v>
       </c>
+      <c r="C16" t="s">
+        <v>128</v>
+      </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1021,13 +1039,13 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1037,348 +1055,357 @@
       <c r="B18" t="s">
         <v>12</v>
       </c>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
       </c>
       <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
         <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
         <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
         <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" t="s">
         <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E40" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" t="s">
         <v>117</v>
-      </c>
-      <c r="F40" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/x0504807/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lewisspurgin/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4FC7E2-1597-C944-8FB5-B9C569E70652}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{6E5304F2-56CB-3F4B-9251-4A5026270A93}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2180" yWindow="1480" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="1480" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="130">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
@@ -1126,6 +1126,9 @@
       <c r="B22" t="s">
         <v>16</v>
       </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
       <c r="D22" t="s">
         <v>72</v>
       </c>
@@ -1139,6 +1142,9 @@
       </c>
       <c r="B23" t="s">
         <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>72</v>

--- a/Manuscript/Contributors.xlsx
+++ b/Manuscript/Contributors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10114"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lewisspurgin/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/x0504807/Documents/Research/SpurginBosse_Hapmap/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{6E5304F2-56CB-3F4B-9251-4A5026270A93}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CB9909-8A09-4F43-80F3-52C6F1DF2A36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="1480" windowWidth="25600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4520" yWindow="1360" windowWidth="26600" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="130">
   <si>
     <t>Adriaensen Frank &lt;frank.adriaensen@uantwerpen.be&gt;,</t>
   </si>
@@ -888,6 +888,9 @@
       <c r="C8" t="s">
         <v>126</v>
       </c>
+      <c r="D8" t="s">
+        <v>72</v>
+      </c>
       <c r="E8" t="s">
         <v>91</v>
       </c>
@@ -1160,6 +1163,9 @@
       <c r="B24" t="s">
         <v>18</v>
       </c>
+      <c r="C24" t="s">
+        <v>127</v>
+      </c>
       <c r="D24" t="s">
         <v>72</v>
       </c>
@@ -1174,6 +1180,9 @@
       <c r="B25" t="s">
         <v>19</v>
       </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
       <c r="D25" t="s">
         <v>72</v>
       </c>
@@ -1205,6 +1214,9 @@
       <c r="B27" t="s">
         <v>21</v>
       </c>
+      <c r="C27" t="s">
+        <v>126</v>
+      </c>
       <c r="D27" t="s">
         <v>72</v>
       </c>
@@ -1219,6 +1231,9 @@
       <c r="B28" t="s">
         <v>33</v>
       </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
       <c r="D28" t="s">
         <v>72</v>
       </c>
@@ -1233,6 +1248,9 @@
       <c r="B29" t="s">
         <v>22</v>
       </c>
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
       <c r="D29" t="s">
         <v>72</v>
       </c>
@@ -1247,6 +1265,9 @@
       <c r="B30" t="s">
         <v>23</v>
       </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
       <c r="D30" t="s">
         <v>72</v>
       </c>
@@ -1261,6 +1282,9 @@
       <c r="B31" t="s">
         <v>34</v>
       </c>
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
       <c r="D31" t="s">
         <v>72</v>
       </c>
@@ -1278,6 +1302,9 @@
       <c r="B32" t="s">
         <v>35</v>
       </c>
+      <c r="C32" t="s">
+        <v>127</v>
+      </c>
       <c r="D32" t="s">
         <v>72</v>
       </c>
@@ -1292,6 +1319,9 @@
       <c r="B33" t="s">
         <v>24</v>
       </c>
+      <c r="C33" t="s">
+        <v>127</v>
+      </c>
       <c r="D33" t="s">
         <v>72</v>
       </c>
@@ -1323,6 +1353,9 @@
       <c r="B35" t="s">
         <v>26</v>
       </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
       <c r="D35" t="s">
         <v>72</v>
       </c>
@@ -1337,6 +1370,9 @@
       <c r="B36" t="s">
         <v>27</v>
       </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
       <c r="D36" t="s">
         <v>72</v>
       </c>
@@ -1362,6 +1398,9 @@
       <c r="B38" t="s">
         <v>29</v>
       </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
       <c r="D38" t="s">
         <v>72</v>
       </c>
@@ -1376,6 +1415,9 @@
       <c r="B39" t="s">
         <v>36</v>
       </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
       <c r="D39" t="s">
         <v>72</v>
       </c>
@@ -1390,6 +1432,9 @@
       <c r="B40" t="s">
         <v>32</v>
       </c>
+      <c r="C40" t="s">
+        <v>126</v>
+      </c>
       <c r="D40" t="s">
         <v>72</v>
       </c>
@@ -1406,6 +1451,9 @@
       </c>
       <c r="B41" t="s">
         <v>123</v>
+      </c>
+      <c r="C41" t="s">
+        <v>127</v>
       </c>
       <c r="D41" t="s">
         <v>72</v>
